--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1048088169286247</v>
+        <v>0.9352187070349397</v>
       </c>
       <c r="C2" t="n">
-        <v>1.172922126776418</v>
+        <v>-0.001373122136744048</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06435914518239003</v>
+        <v>1.66365536387497</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5944555028197163</v>
+        <v>0.9025705429363163</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4856033645066357</v>
+        <v>0.9544746231217318</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08491901188132</v>
+        <v>-1.09400397186656</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.002995295048665642</v>
+        <v>-1.174974030888932</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1263115410512186</v>
+        <v>0.5121346798762368</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.9988829331061516</v>
+        <v>-0.1191910548248049</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.06761523616648323</v>
+        <v>-2.338554802721806</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8334432691306404</v>
+        <v>0.4313068139683647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9181223185958434</v>
+        <v>1.184880470558155</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9357126263176084</v>
+        <v>1.078134645956567</v>
       </c>
       <c r="C5" t="n">
-        <v>0.729240140273913</v>
+        <v>-1.918806426549788</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9635429205119208</v>
+        <v>-1.498754120730269</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.11159270068825</v>
+        <v>0.76809061231028</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.1043602853134394</v>
+        <v>0.277589137231383</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.246169753979054</v>
+        <v>-0.1780250155472321</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1327114004289747</v>
+        <v>0.9962995182238688</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2675835156064695</v>
+        <v>-1.063625358745883</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2224474097974269</v>
+        <v>0.9287319707987909</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.235791162643925</v>
+        <v>0.2903328126734079</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5856543462901105</v>
+        <v>-1.649659571975333</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6545799988423944</v>
+        <v>-1.254437285423561</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9352187070349397</v>
+        <v>-0.2019546177877362</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.001373122136744048</v>
+        <v>0.7813845515511666</v>
       </c>
       <c r="D2" t="n">
-        <v>1.66365536387497</v>
+        <v>-1.267643711415489</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9025705429363163</v>
+        <v>0.7002251505592813</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9544746231217318</v>
+        <v>-1.456883334505886</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.09400397186656</v>
+        <v>-1.605704344297131</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.174974030888932</v>
+        <v>0.4199866333881853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5121346798762368</v>
+        <v>-1.179554002947612</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1191910548248049</v>
+        <v>-0.7459984684046379</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.338554802721806</v>
+        <v>-1.909206903928778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4313068139683647</v>
+        <v>-0.3330460217646233</v>
       </c>
       <c r="E4" t="n">
-        <v>1.184880470558155</v>
+        <v>-1.400492856091534</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>1.078134645956567</v>
+        <v>0.9946924250081572</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.918806426549788</v>
+        <v>-0.7482303079831567</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.498754120730269</v>
+        <v>-0.2809730454299257</v>
       </c>
       <c r="E5" t="n">
-        <v>0.76809061231028</v>
+        <v>1.069498309775552</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.277589137231383</v>
+        <v>1.014702838176465</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1780250155472321</v>
+        <v>-1.848645057114111</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9962995182238688</v>
+        <v>0.8620492751637883</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.063625358745883</v>
+        <v>1.57578834765567</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9287319707987909</v>
+        <v>-1.544934643230672</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2903328126734079</v>
+        <v>-1.405809747417064</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.649659571975333</v>
+        <v>-0.2474515823248684</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.254437285423561</v>
+        <v>1.31714644024619</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2019546177877362</v>
+        <v>0.4729052627743336</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7813845515511666</v>
+        <v>-0.1037678454548301</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.267643711415489</v>
+        <v>-0.02260118391139074</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7002251505592813</v>
+        <v>-0.2126508543302386</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.456883334505886</v>
+        <v>0.4126684941003931</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.605704344297131</v>
+        <v>-1.128429096744302</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4199866333881853</v>
+        <v>1.108637507826338</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.179554002947612</v>
+        <v>-0.7987912224738537</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.7459984684046379</v>
+        <v>0.5896813674673649</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.909206903928778</v>
+        <v>-1.810701044017247</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3330460217646233</v>
+        <v>-2.083407704406923</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.400492856091534</v>
+        <v>3.495957053431018</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9946924250081572</v>
+        <v>0.06572810504590865</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.7482303079831567</v>
+        <v>0.3363123763943717</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2809730454299257</v>
+        <v>-0.8329568498499225</v>
       </c>
       <c r="E5" t="n">
-        <v>1.069498309775552</v>
+        <v>0.1669023392712801</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>1.014702838176465</v>
+        <v>2.339807567890972</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.848645057114111</v>
+        <v>-0.3474654699390594</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8620492751637883</v>
+        <v>-0.9321077937180758</v>
       </c>
       <c r="E6" t="n">
-        <v>1.57578834765567</v>
+        <v>0.2098083885297142</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.544934643230672</v>
+        <v>2.225196049749889</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.405809747417064</v>
+        <v>0.1199365474522753</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2474515823248684</v>
+        <v>-1.015923465577589</v>
       </c>
       <c r="E7" t="n">
-        <v>1.31714644024619</v>
+        <v>0.2180302512561401</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4729052627743336</v>
+        <v>-0.5445764182335437</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1037678454548301</v>
+        <v>0.7713202362842739</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02260118391139074</v>
+        <v>-1.492919017908787</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2126508543302386</v>
+        <v>-0.6504824407636411</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4126684941003931</v>
+        <v>-0.4362094807458344</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.128429096744302</v>
+        <v>-0.7042799281560806</v>
       </c>
       <c r="D3" t="n">
-        <v>1.108637507826338</v>
+        <v>-0.03086113539358691</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7987912224738537</v>
+        <v>0.09918976072613263</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5896813674673649</v>
+        <v>-1.03617000003578</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.810701044017247</v>
+        <v>-1.462805074136837</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.083407704406923</v>
+        <v>0.8143847174772921</v>
       </c>
       <c r="E4" t="n">
-        <v>3.495957053431018</v>
+        <v>-1.456961512691042</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06572810504590865</v>
+        <v>-0.1781616616894493</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3363123763943717</v>
+        <v>-0.1614058786069431</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8329568498499225</v>
+        <v>0.4549817449321585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1669023392712801</v>
+        <v>0.6198409669948636</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>2.339807567890972</v>
+        <v>-0.5591020639831538</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3474654699390594</v>
+        <v>-0.8425940315717046</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9321077937180758</v>
+        <v>0.7171240443064741</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2098083885297142</v>
+        <v>-1.981516885986369</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>2.225196049749889</v>
+        <v>0.6869210772450475</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1199365474522753</v>
+        <v>-1.265590957768281</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.015923465577589</v>
+        <v>2.009927632900349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2180302512561401</v>
+        <v>-0.7214981816185576</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.5445764182335437</v>
+        <v>0.9841387027764817</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7713202362842739</v>
+        <v>2.171894360914639</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.492919017908787</v>
+        <v>-0.1403302192497937</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6504824407636411</v>
+        <v>0.2260579869747807</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.4362094807458344</v>
+        <v>-1.110701185096772</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.7042799281560806</v>
+        <v>-0.3953309298862316</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03086113539358691</v>
+        <v>0.7177952182078766</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09918976072613263</v>
+        <v>0.4238994769130846</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.03617000003578</v>
+        <v>0.4644398077910024</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.462805074136837</v>
+        <v>-0.5582089376957327</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8143847174772921</v>
+        <v>0.5598714977846619</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.456961512691042</v>
+        <v>0.2768832699763518</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1781616616894493</v>
+        <v>-0.2780090912933055</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1614058786069431</v>
+        <v>-1.043254618414274</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4549817449321585</v>
+        <v>0.8417332446002769</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6198409669948636</v>
+        <v>0.9839057641004586</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.5591020639831538</v>
+        <v>-0.07496486421528138</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8425940315717046</v>
+        <v>-1.034831696511499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7171240443064741</v>
+        <v>-0.5832045357313383</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.981516885986369</v>
+        <v>-1.314818253064014</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6869210772450475</v>
+        <v>2.096679086344856</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.265590957768281</v>
+        <v>-0.62352647864837</v>
       </c>
       <c r="D7" t="n">
-        <v>2.009927632900349</v>
+        <v>-0.0308311521261816</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7214981816185576</v>
+        <v>-0.5608935056363158</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9841387027764817</v>
+        <v>0.359016644562817</v>
       </c>
       <c r="C2" t="n">
-        <v>2.171894360914639</v>
+        <v>0.9329612897425531</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1403302192497937</v>
+        <v>-0.4746955947096708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2260579869747807</v>
+        <v>-1.875599316095523</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.110701185096772</v>
+        <v>0.5232918369392987</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3953309298862316</v>
+        <v>1.175308695708722</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7177952182078766</v>
+        <v>0.6079297963413701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4238994769130846</v>
+        <v>0.6615209520999592</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4644398077910024</v>
+        <v>-0.7178990143283585</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5582089376957327</v>
+        <v>0.8139438006264663</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5598714977846619</v>
+        <v>1.131600072750221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2768832699763518</v>
+        <v>0.7253937102799825</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2780090912933055</v>
+        <v>-0.2981356316340165</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.043254618414274</v>
+        <v>0.1297408836773878</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8417332446002769</v>
+        <v>0.4274397420243007</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9839057641004586</v>
+        <v>0.149737424761306</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.07496486421528138</v>
+        <v>0.4673825338436416</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.034831696511499</v>
+        <v>1.92756365391963</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5832045357313383</v>
+        <v>-0.01107604884078455</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.314818253064014</v>
+        <v>2.212832980272515</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>2.096679086344856</v>
+        <v>-0.9222328895397666</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.62352647864837</v>
+        <v>-1.326416779349253</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0308311521261816</v>
+        <v>2.176886226184851</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5608935056363158</v>
+        <v>-0.7712360412536583</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.359016644562817</v>
+        <v>0.7803162248556464</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9329612897425531</v>
+        <v>-0.2114025776186826</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4746955947096708</v>
+        <v>-0.1700352235282437</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.875599316095523</v>
+        <v>0.4588734420723287</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5232918369392987</v>
+        <v>-0.2786063781781856</v>
       </c>
       <c r="C3" t="n">
-        <v>1.175308695708722</v>
+        <v>-1.864621969532842</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6079297963413701</v>
+        <v>1.089225726364528</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6615209520999592</v>
+        <v>0.3938787100804268</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.7178990143283585</v>
+        <v>0.05950292266195247</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8139438006264663</v>
+        <v>0.4074128998261193</v>
       </c>
       <c r="D4" t="n">
-        <v>1.131600072750221</v>
+        <v>-0.1798027701412459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7253937102799825</v>
+        <v>0.1290871679829807</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2981356316340165</v>
+        <v>-1.000394696338305</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1297408836773878</v>
+        <v>-0.9615201027173934</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4274397420243007</v>
+        <v>-0.7199819068419548</v>
       </c>
       <c r="E5" t="n">
-        <v>0.149737424761306</v>
+        <v>1.316969832959628</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4673825338436416</v>
+        <v>-0.2457819711678138</v>
       </c>
       <c r="C6" t="n">
-        <v>1.92756365391963</v>
+        <v>-0.03535189225425612</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01107604884078455</v>
+        <v>-0.8640555324115493</v>
       </c>
       <c r="E6" t="n">
-        <v>2.212832980272515</v>
+        <v>-1.454735371341725</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.9222328895397666</v>
+        <v>-0.5285731966033534</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.326416779349253</v>
+        <v>0.7866786279822843</v>
       </c>
       <c r="D7" t="n">
-        <v>2.176886226184851</v>
+        <v>-0.2811008802616334</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7712360412536583</v>
+        <v>-1.203809575006251</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7803162248556464</v>
+        <v>-0.9064468033486903</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2114025776186826</v>
+        <v>-0.2431023414533725</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1700352235282437</v>
+        <v>-1.333690641366363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4588734420723287</v>
+        <v>1.915504822243281</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2786063781781856</v>
+        <v>-0.2508532215159994</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.864621969532842</v>
+        <v>0.3627928931083719</v>
       </c>
       <c r="D3" t="n">
-        <v>1.089225726364528</v>
+        <v>-1.123841146569927</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3938787100804268</v>
+        <v>-3.808239521217733</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05950292266195247</v>
+        <v>-0.6572303988227776</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4074128998261193</v>
+        <v>0.2657301553658582</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1798027701412459</v>
+        <v>0.1620238532870789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1290871679829807</v>
+        <v>0.5630356030916549</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.000394696338305</v>
+        <v>0.1477604475263346</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9615201027173934</v>
+        <v>-0.9218885822671985</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7199819068419548</v>
+        <v>-1.467397529926754</v>
       </c>
       <c r="E5" t="n">
-        <v>1.316969832959628</v>
+        <v>-0.06736140396615729</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2457819711678138</v>
+        <v>-0.7166441361517705</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.03535189225425612</v>
+        <v>0.4948103074476362</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8640555324115493</v>
+        <v>0.5635935442400524</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.454735371341725</v>
+        <v>-0.06900257693132446</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5285731966033534</v>
+        <v>-1.700208305351069</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7866786279822843</v>
+        <v>-1.209805020169138</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2811008802616334</v>
+        <v>-1.277771318543533</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.203809575006251</v>
+        <v>0.7512199727923619</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.9064468033486903</v>
+        <v>-0.242388434154328</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2431023414533725</v>
+        <v>-1.018610580541968</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.333690641366363</v>
+        <v>1.820653991464779</v>
       </c>
       <c r="E2" t="n">
-        <v>1.915504822243281</v>
+        <v>0.4681584519745186</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2508532215159994</v>
+        <v>-1.85290865127816</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3627928931083719</v>
+        <v>-0.8912292365052283</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.123841146569927</v>
+        <v>-0.9193281755808789</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.808239521217733</v>
+        <v>-0.1923743660330988</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.6572303988227776</v>
+        <v>0.1984851380133643</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2657301553658582</v>
+        <v>-0.5265175336303222</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1620238532870789</v>
+        <v>-0.4319704416163208</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5630356030916549</v>
+        <v>-0.8546555320623469</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1477604475263346</v>
+        <v>-0.5138959095868534</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9218885822671985</v>
+        <v>-0.007603017342082699</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.467397529926754</v>
+        <v>0.6960778282786531</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06736140396615729</v>
+        <v>-0.09453788736410136</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.7166441361517705</v>
+        <v>-0.5857957108702699</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4948103074476362</v>
+        <v>-0.2352906991731916</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5635935442400524</v>
+        <v>0.1344180962509313</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06900257693132446</v>
+        <v>-1.313767755879661</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.700208305351069</v>
+        <v>0.1379556722339077</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.209805020169138</v>
+        <v>-1.027753217587483</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.277771318543533</v>
+        <v>-0.4790981879599896</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7512199727923619</v>
+        <v>0.389260015439571</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.242388434154328</v>
+        <v>-0.270551668180294</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.018610580541968</v>
+        <v>-0.6831467880936301</v>
       </c>
       <c r="D2" t="n">
-        <v>1.820653991464779</v>
+        <v>-0.109419214077972</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4681584519745186</v>
+        <v>-0.6791048548557256</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.85290865127816</v>
+        <v>-1.306076716758247</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.8912292365052283</v>
+        <v>0.4464813519096857</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9193281755808789</v>
+        <v>1.028822189323318</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1923743660330988</v>
+        <v>0.2065811328292699</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1984851380133643</v>
+        <v>-0.4197406798382062</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5265175336303222</v>
+        <v>-0.09581979177568327</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4319704416163208</v>
+        <v>-0.1474464200291595</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8546555320623469</v>
+        <v>-0.2893329636704884</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.5138959095868534</v>
+        <v>0.7464863321972169</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.007603017342082699</v>
+        <v>-0.4837075191055288</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6960778282786531</v>
+        <v>0.2486899814442152</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09453788736410136</v>
+        <v>-0.1384121044775351</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.5857957108702699</v>
+        <v>0.6830862902069962</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2352906991731916</v>
+        <v>0.5239928253092234</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1344180962509313</v>
+        <v>-0.8603777128962032</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.313767755879661</v>
+        <v>0.01796108567372689</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1379556722339077</v>
+        <v>-1.532780879841526</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.027753217587483</v>
+        <v>-0.9543694520279542</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4790981879599896</v>
+        <v>-1.223631979877309</v>
       </c>
       <c r="E7" t="n">
-        <v>0.389260015439571</v>
+        <v>0.6182008558694922</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.270551668180294</v>
+        <v>-0.4806153583932788</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6831467880936301</v>
+        <v>-0.1571760794728942</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.109419214077972</v>
+        <v>2.354932623137785</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6791048548557256</v>
+        <v>-0.9767506610415548</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.306076716758247</v>
+        <v>0.3445524899340706</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4464813519096857</v>
+        <v>1.508410958510117</v>
       </c>
       <c r="D3" t="n">
-        <v>1.028822189323318</v>
+        <v>0.2864883211142816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2065811328292699</v>
+        <v>-0.8563568097652667</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4197406798382062</v>
+        <v>0.1404041503460335</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09581979177568327</v>
+        <v>-1.532440218962135</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1474464200291595</v>
+        <v>-0.1705312170631469</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2893329636704884</v>
+        <v>-0.1600179158277677</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7464863321972169</v>
+        <v>1.187501101573462</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4837075191055288</v>
+        <v>-0.6073947370333788</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2486899814442152</v>
+        <v>-0.9852331561313258</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1384121044775351</v>
+        <v>-1.264206915958874</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6830862902069962</v>
+        <v>0.1730979211603366</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5239928253092234</v>
+        <v>0.6330520421537142</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8603777128962032</v>
+        <v>0.3933066647289258</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01796108567372689</v>
+        <v>1.113143120735095</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.532780879841526</v>
+        <v>-0.4339296431976158</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.9543694520279542</v>
+        <v>-0.009299136671749393</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.223631979877309</v>
+        <v>-0.3825700674351345</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6182008558694922</v>
+        <v>0.2792835603049687</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4806153583932788</v>
+        <v>-0.2390102033246818</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1571760794728942</v>
+        <v>-0.5342613325094243</v>
       </c>
       <c r="D2" t="n">
-        <v>2.354932623137785</v>
+        <v>0.8139138985301529</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9767506610415548</v>
+        <v>-0.6761424063737322</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3445524899340706</v>
+        <v>0.9078288217807132</v>
       </c>
       <c r="C3" t="n">
-        <v>1.508410958510117</v>
+        <v>0.467445255630054</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2864883211142816</v>
+        <v>-0.474106533739666</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8563568097652667</v>
+        <v>-2.123993535764701</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1404041503460335</v>
+        <v>0.09352678336910272</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.532440218962135</v>
+        <v>0.1398253236962124</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1705312170631469</v>
+        <v>-0.01679741364021368</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1600179158277677</v>
+        <v>0.1622209246393055</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>1.187501101573462</v>
+        <v>-0.2898841979965126</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.6073947370333788</v>
+        <v>-0.4896505509382229</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9852331561313258</v>
+        <v>0.5255057285334751</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.264206915958874</v>
+        <v>0.4710561850259783</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1730979211603366</v>
+        <v>0.5282083164732527</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6330520421537142</v>
+        <v>-3.120141525977356</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3933066647289258</v>
+        <v>-1.372328877163688</v>
       </c>
       <c r="E6" t="n">
-        <v>1.113143120735095</v>
+        <v>0.332817437808876</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4339296431976158</v>
+        <v>-1.239138431900284</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.009299136671749393</v>
+        <v>-0.2097344584713825</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3825700674351345</v>
+        <v>-1.278726284144416</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2792835603049687</v>
+        <v>0.8494310313753075</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2390102033246818</v>
+        <v>-0.3258969698432931</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5342613325094243</v>
+        <v>0.584415888607158</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8139138985301529</v>
+        <v>-0.5103915454178257</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6761424063737322</v>
+        <v>0.1734878383444022</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9078288217807132</v>
+        <v>-0.1593027279453681</v>
       </c>
       <c r="C3" t="n">
-        <v>0.467445255630054</v>
+        <v>0.7947240094659656</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.474106533739666</v>
+        <v>1.877631752639574</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.123993535764701</v>
+        <v>1.537211764269852</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09352678336910272</v>
+        <v>1.10495220952289</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1398253236962124</v>
+        <v>1.922451443813626</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01679741364021368</v>
+        <v>-0.8945438809584288</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1622209246393055</v>
+        <v>-0.2096208695796269</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2898841979965126</v>
+        <v>0.5471283202872932</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4896505509382229</v>
+        <v>1.036383010218733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5255057285334751</v>
+        <v>-0.07474864252822973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4710561850259783</v>
+        <v>0.7861937190048071</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5282083164732527</v>
+        <v>0.4630101413428567</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.120141525977356</v>
+        <v>0.7206575741050347</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.372328877163688</v>
+        <v>-1.498894841514097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.332817437808876</v>
+        <v>0.3518824092603784</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.239138431900284</v>
+        <v>-0.7961317288939265</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2097344584713825</v>
+        <v>-0.5345674504012921</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.278726284144416</v>
+        <v>0.4339188105847851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8494310313753075</v>
+        <v>-0.8248035413438982</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.3258969698432931</v>
+        <v>-1.59163484309394</v>
       </c>
       <c r="C2" t="n">
-        <v>0.584415888607158</v>
+        <v>0.8214771567947554</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5103915454178257</v>
+        <v>-0.2161751007728094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1734878383444022</v>
+        <v>-0.7649370737908013</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.1593027279453681</v>
+        <v>-0.8569351879470629</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7947240094659656</v>
+        <v>-0.1799387621624765</v>
       </c>
       <c r="D3" t="n">
-        <v>1.877631752639574</v>
+        <v>2.060608579070481</v>
       </c>
       <c r="E3" t="n">
-        <v>1.537211764269852</v>
+        <v>-1.221545103262129</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>1.10495220952289</v>
+        <v>-0.552915947782922</v>
       </c>
       <c r="C4" t="n">
-        <v>1.922451443813626</v>
+        <v>1.059453248854095</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8945438809584288</v>
+        <v>0.6490188987966981</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2096208695796269</v>
+        <v>-0.000577517308157602</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5471283202872932</v>
+        <v>0.8516540668024809</v>
       </c>
       <c r="C5" t="n">
-        <v>1.036383010218733</v>
+        <v>0.2679587996812486</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07474864252822973</v>
+        <v>0.3244383684042729</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7861937190048071</v>
+        <v>0.5073000684400111</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4630101413428567</v>
+        <v>-0.162875868232187</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7206575741050347</v>
+        <v>-0.8076413258030926</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.498894841514097</v>
+        <v>-0.6177147834672966</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3518824092603784</v>
+        <v>-0.7203858406020796</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.7961317288939265</v>
+        <v>-1.448479189662004</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5345674504012921</v>
+        <v>-0.01090006283553634</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4339188105847851</v>
+        <v>-0.1991870500622152</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8248035413438982</v>
+        <v>-0.4903668836412669</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.59163484309394</v>
+        <v>1.222711111893849</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8214771567947554</v>
+        <v>-0.145389445136528</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2161751007728094</v>
+        <v>0.2963710615617425</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7649370737908013</v>
+        <v>0.6537051907068079</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.8569351879470629</v>
+        <v>0.9988037016425658</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1799387621624765</v>
+        <v>0.1856877659467565</v>
       </c>
       <c r="D3" t="n">
-        <v>2.060608579070481</v>
+        <v>0.6098978807720461</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.221545103262129</v>
+        <v>0.3357888373139365</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.552915947782922</v>
+        <v>-1.596976358256704</v>
       </c>
       <c r="C4" t="n">
-        <v>1.059453248854095</v>
+        <v>-0.8606747324309149</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6490188987966981</v>
+        <v>-0.5304989744320453</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.000577517308157602</v>
+        <v>0.2637443342043887</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8516540668024809</v>
+        <v>-0.3382384590578161</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2679587996812486</v>
+        <v>-0.2004433075630442</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3244383684042729</v>
+        <v>0.5176664748539953</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5073000684400111</v>
+        <v>0.8288738745548744</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.162875868232187</v>
+        <v>0.4836363979681875</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8076413258030926</v>
+        <v>0.3977891640373667</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6177147834672966</v>
+        <v>0.2332118565076919</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7203858406020796</v>
+        <v>-1.940194469475266</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.448479189662004</v>
+        <v>1.460408828120254</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.01090006283553634</v>
+        <v>0.0697589596859968</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1991870500622152</v>
+        <v>-0.2397788799820098</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4903668836412669</v>
+        <v>0.5100332086805209</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>1.222711111893849</v>
+        <v>-0.02943687671986546</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.145389445136528</v>
+        <v>0.3935578199907366</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2963710615617425</v>
+        <v>-1.086138417305195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6537051907068079</v>
+        <v>-0.4834388490210777</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9988037016425658</v>
+        <v>-0.5648131488318124</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1856877659467565</v>
+        <v>-0.09554348498115868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6098978807720461</v>
+        <v>0.1206207604242615</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3357888373139365</v>
+        <v>-0.6796033415186687</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.596976358256704</v>
+        <v>0.1336099265530282</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.8606747324309149</v>
+        <v>1.074254422399638</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5304989744320453</v>
+        <v>0.808522556977342</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2637443342043887</v>
+        <v>-0.2649069220761383</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.3382384590578161</v>
+        <v>0.4506316479881978</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2004433075630442</v>
+        <v>-1.664838664498379</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5176664748539953</v>
+        <v>-0.7674214519498668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8288738745548744</v>
+        <v>0.3928203375811432</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4836363979681875</v>
+        <v>-0.3198421812847109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3977891640373667</v>
+        <v>0.992180357631447</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2332118565076919</v>
+        <v>0.1056894797590061</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.940194469475266</v>
+        <v>-0.3609883837492341</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>1.460408828120254</v>
+        <v>0.4439402930379653</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0697589596859968</v>
+        <v>0.5579487915953139</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2397788799820098</v>
+        <v>1.334792126363695</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5100332086805209</v>
+        <v>-2.206880213471723</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.02943687671986546</v>
+        <v>0.9522499959338965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3935578199907366</v>
+        <v>-0.4437334524785068</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.086138417305195</v>
+        <v>-1.072061925804478</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4834388490210777</v>
+        <v>-0.1470883903329481</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5648131488318124</v>
+        <v>-0.5379207944954946</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.09554348498115868</v>
+        <v>-1.742540052157531</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1206207604242615</v>
+        <v>0.3650975418502375</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6796033415186687</v>
+        <v>-0.8394553452163601</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1336099265530282</v>
+        <v>0.922261906657962</v>
       </c>
       <c r="C4" t="n">
-        <v>1.074254422399638</v>
+        <v>-0.2004902019380766</v>
       </c>
       <c r="D4" t="n">
-        <v>0.808522556977342</v>
+        <v>-1.22946510246538</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2649069220761383</v>
+        <v>0.9196081710989928</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4506316479881978</v>
+        <v>0.3813323268676455</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.664838664498379</v>
+        <v>1.405801782725201</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7674214519498668</v>
+        <v>-0.5435542402969361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3928203375811432</v>
+        <v>1.36138534336518</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.3198421812847109</v>
+        <v>-0.9439484321383976</v>
       </c>
       <c r="C6" t="n">
-        <v>0.992180357631447</v>
+        <v>1.005759047441602</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1056894797590061</v>
+        <v>0.3064037318836543</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3609883837492341</v>
+        <v>-1.772373089969851</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4439402930379653</v>
+        <v>0.757504900640422</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5579487915953139</v>
+        <v>0.6361221705391351</v>
       </c>
       <c r="D7" t="n">
-        <v>1.334792126363695</v>
+        <v>1.871436351297681</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.206880213471723</v>
+        <v>2.225619391061281</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9522499959338965</v>
+        <v>0.9767245086957911</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.4437334524785068</v>
+        <v>-0.1317932609353559</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.072061925804478</v>
+        <v>-0.3402364390505132</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1470883903329481</v>
+        <v>0.847997415903545</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.5379207944954946</v>
+        <v>0.1014356272092944</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.742540052157531</v>
+        <v>-1.028809272071495</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3650975418502375</v>
+        <v>0.258410694635856</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8394553452163601</v>
+        <v>-0.926824994097378</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.922261906657962</v>
+        <v>1.59555028409481</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2004902019380766</v>
+        <v>0.07040766034917829</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.22946510246538</v>
+        <v>0.189495640658909</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9196081710989928</v>
+        <v>0.7998115527651209</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3813323268676455</v>
+        <v>0.04430367022625776</v>
       </c>
       <c r="C5" t="n">
-        <v>1.405801782725201</v>
+        <v>0.8790304106226687</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5435542402969361</v>
+        <v>0.1935328634331355</v>
       </c>
       <c r="E5" t="n">
-        <v>1.36138534336518</v>
+        <v>-0.06324784278242838</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.9439484321383976</v>
+        <v>-1.573837140821436</v>
       </c>
       <c r="C6" t="n">
-        <v>1.005759047441602</v>
+        <v>-1.486218384825679</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3064037318836543</v>
+        <v>-1.210954263086466</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.772373089969851</v>
+        <v>0.7183808364030269</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.757504900640422</v>
+        <v>0.2162700658395426</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6361221705391351</v>
+        <v>-0.4124543328063587</v>
       </c>
       <c r="D7" t="n">
-        <v>1.871436351297681</v>
+        <v>-1.791547006913543</v>
       </c>
       <c r="E7" t="n">
-        <v>2.225619391061281</v>
+        <v>-1.7065306978888</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9767245086957911</v>
+        <v>-0.9386289141502724</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1317932609353559</v>
+        <v>1.20906790551156</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3402364390505132</v>
+        <v>-0.1412118186861032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.847997415903545</v>
+        <v>1.273618223544597</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1014356272092944</v>
+        <v>1.552771748266324</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.028809272071495</v>
+        <v>-0.3061694649224153</v>
       </c>
       <c r="D3" t="n">
-        <v>0.258410694635856</v>
+        <v>1.471515734501768</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.926824994097378</v>
+        <v>-0.1314885438754443</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>1.59555028409481</v>
+        <v>0.4753345634040359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.07040766034917829</v>
+        <v>0.5736819919081384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.189495640658909</v>
+        <v>-0.215785305445444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7998115527651209</v>
+        <v>0.3792650017617193</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04430367022625776</v>
+        <v>-1.396777326215749</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8790304106226687</v>
+        <v>-0.1797770007864626</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1935328634331355</v>
+        <v>-0.9110798070910088</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06324784278242838</v>
+        <v>-0.4032622499503755</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.573837140821436</v>
+        <v>0.8152969891392913</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.486218384825679</v>
+        <v>-0.04067651927263021</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.210954263086466</v>
+        <v>0.6296333558149593</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7183808364030269</v>
+        <v>0.07783872776090521</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2162700658395426</v>
+        <v>-0.4413058993224883</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4124543328063587</v>
+        <v>-1.138453871636786</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.791547006913543</v>
+        <v>-0.6569282027140103</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7065306978888</v>
+        <v>0.08167367462486148</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.9386289141502724</v>
+        <v>1.108664852288966</v>
       </c>
       <c r="C2" t="n">
-        <v>1.20906790551156</v>
+        <v>0.6721005180865988</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1412118186861032</v>
+        <v>0.1719643429998049</v>
       </c>
       <c r="E2" t="n">
-        <v>1.273618223544597</v>
+        <v>0.08281743393205877</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>1.552771748266324</v>
+        <v>-0.6053080225127427</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3061694649224153</v>
+        <v>1.182816656908705</v>
       </c>
       <c r="D3" t="n">
-        <v>1.471515734501768</v>
+        <v>0.3929042963765</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1314885438754443</v>
+        <v>0.3800075650022802</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4753345634040359</v>
+        <v>0.9427637996456179</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5736819919081384</v>
+        <v>-0.2398700035168038</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.215785305445444</v>
+        <v>-0.8184300003427502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3792650017617193</v>
+        <v>-0.5101541724268648</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.396777326215749</v>
+        <v>1.210620077925699</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1797770007864626</v>
+        <v>-1.008464878633964</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9110798070910088</v>
+        <v>-0.1833465372128422</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4032622499503755</v>
+        <v>-0.1008423961705043</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8152969891392913</v>
+        <v>1.450964809103295</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.04067651927263021</v>
+        <v>-0.983637600753303</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6296333558149593</v>
+        <v>-0.6005354789949336</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07783872776090521</v>
+        <v>0.4819817989528339</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.4413058993224883</v>
+        <v>-1.125864292907454</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.138453871636786</v>
+        <v>0.3725683686125291</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6569282027140103</v>
+        <v>-1.094641000687003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08167367462486148</v>
+        <v>-0.2512844390040445</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>1.108664852288966</v>
+        <v>1.95059231048172</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6721005180865988</v>
+        <v>0.5906047700861874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1719643429998049</v>
+        <v>1.102965893472319</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08281743393205877</v>
+        <v>-0.4060994535804777</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.6053080225127427</v>
+        <v>1.222652610655796</v>
       </c>
       <c r="C3" t="n">
-        <v>1.182816656908705</v>
+        <v>-0.3786850443788022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3929042963765</v>
+        <v>-0.548266628401969</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3800075650022802</v>
+        <v>0.558447920551024</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9427637996456179</v>
+        <v>-0.4133212217470191</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2398700035168038</v>
+        <v>-0.02401190072922076</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8184300003427502</v>
+        <v>-0.06522368049093821</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5101541724268648</v>
+        <v>1.023622294774682</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>1.210620077925699</v>
+        <v>-0.4216416403469183</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.008464878633964</v>
+        <v>0.9773938940483762</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1833465372128422</v>
+        <v>-0.8498432843925723</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1008423961705043</v>
+        <v>0.06436558387951549</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>1.450964809103295</v>
+        <v>0.4405746920637437</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.983637600753303</v>
+        <v>1.992232634915913</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6005354789949336</v>
+        <v>-1.237873882677241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4819817989528339</v>
+        <v>1.245242602409949</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.125864292907454</v>
+        <v>0.1064904763665445</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3725683686125291</v>
+        <v>0.9105749609872492</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.094641000687003</v>
+        <v>-0.7752227449242748</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2512844390040445</v>
+        <v>-0.3787971153629178</v>
       </c>
     </row>
   </sheetData>

--- a/lab/files/01-reviewPython/test.xlsx
+++ b/lab/files/01-reviewPython/test.xlsx
@@ -447,16 +447,16 @@
         <v>41275</v>
       </c>
       <c r="B2" t="n">
-        <v>1.95059231048172</v>
+        <v>1.373085795648902</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5906047700861874</v>
+        <v>-0.3505772499087497</v>
       </c>
       <c r="D2" t="n">
-        <v>1.102965893472319</v>
+        <v>-2.516333835914006</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4060994535804777</v>
+        <v>-0.7034515481521132</v>
       </c>
     </row>
     <row r="3">
@@ -464,16 +464,16 @@
         <v>41276</v>
       </c>
       <c r="B3" t="n">
-        <v>1.222652610655796</v>
+        <v>-1.018008830512416</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3786850443788022</v>
+        <v>0.6981457097247288</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.548266628401969</v>
+        <v>-0.2310882647603957</v>
       </c>
       <c r="E3" t="n">
-        <v>0.558447920551024</v>
+        <v>0.4571291686938462</v>
       </c>
     </row>
     <row r="4">
@@ -481,16 +481,16 @@
         <v>41277</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4133212217470191</v>
+        <v>0.9706433197151764</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.02401190072922076</v>
+        <v>2.081832768268028</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.06522368049093821</v>
+        <v>-1.691717850626791</v>
       </c>
       <c r="E4" t="n">
-        <v>1.023622294774682</v>
+        <v>0.2186686241957022</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         <v>41278</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4216416403469183</v>
+        <v>-2.135713330076228</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9773938940483762</v>
+        <v>0.3315713525235272</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8498432843925723</v>
+        <v>-1.711998346203712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06436558387951549</v>
+        <v>0.3289135273351144</v>
       </c>
     </row>
     <row r="6">
@@ -515,16 +515,16 @@
         <v>41279</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4405746920637437</v>
+        <v>-0.7344013377438335</v>
       </c>
       <c r="C6" t="n">
-        <v>1.992232634915913</v>
+        <v>0.9729259978285529</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.237873882677241</v>
+        <v>-0.1870248206252099</v>
       </c>
       <c r="E6" t="n">
-        <v>1.245242602409949</v>
+        <v>-0.3088511527567074</v>
       </c>
     </row>
     <row r="7">
@@ -532,16 +532,16 @@
         <v>41280</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1064904763665445</v>
+        <v>1.237275409543428</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9105749609872492</v>
+        <v>-1.110152820465591</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7752227449242748</v>
+        <v>0.2710881438414633</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3787971153629178</v>
+        <v>-1.958957943689633</v>
       </c>
     </row>
   </sheetData>
